--- a/backend/InternLink/InternLink.API/Templates/InternshipExportTemplate.xlsx
+++ b/backend/InternLink/InternLink.API/Templates/InternshipExportTemplate.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\internlink\backend\InternLink\InternLink.API\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\InternLink\backend\InternLink\InternLink.API\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD88742D-42DB-426E-B6C9-49FB8B7F072E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1969052-3C90-4C2E-B0DE-45C0DD77BC37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DANH SÁCH (2)" sheetId="4" r:id="rId1"/>
@@ -122,9 +122,6 @@
     <t>NỘP BC</t>
   </si>
   <si>
-    <t>DANH SÁCH SINH VIÊN THỰC TẬP TẠI DOANH NGHIỆP KHÓA C23</t>
-  </si>
-  <si>
     <t>C23A.TH2</t>
   </si>
   <si>
@@ -490,6 +487,9 @@
   </si>
   <si>
     <t>DANH SÁCH SINH VIÊN THỰC TẬP TẠI DOANH NGHIỆP</t>
+  </si>
+  <si>
+    <t>DANH SÁCH SINH VIÊN THỰC TẬP TẠI DOANH NGHIỆP KHÓA {Khoa}</t>
   </si>
 </sst>
 </file>
@@ -954,14 +954,14 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1260,39 +1260,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" s="3" customFormat="1" ht="39.75" customHeight="1">
-      <c r="A1" s="60" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="60"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="60"/>
-      <c r="R1" s="60"/>
-      <c r="S1" s="60"/>
-      <c r="T1" s="60"/>
-      <c r="U1" s="60"/>
+      <c r="A1" s="59" t="s">
+        <v>148</v>
+      </c>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="59"/>
+      <c r="O1" s="59"/>
+      <c r="P1" s="59"/>
+      <c r="Q1" s="59"/>
+      <c r="R1" s="59"/>
+      <c r="S1" s="59"/>
+      <c r="T1" s="59"/>
+      <c r="U1" s="59"/>
     </row>
     <row r="2" spans="1:21" ht="35.85" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>1</v>
@@ -1310,16 +1310,16 @@
         <v>23</v>
       </c>
       <c r="I2" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="J2" s="35" t="s">
         <v>124</v>
       </c>
-      <c r="J2" s="35" t="s">
-        <v>125</v>
-      </c>
       <c r="K2" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="L2" s="37" t="s">
         <v>127</v>
-      </c>
-      <c r="L2" s="37" t="s">
-        <v>128</v>
       </c>
       <c r="M2" s="29" t="s">
         <v>14</v>
@@ -1340,7 +1340,7 @@
         <v>19</v>
       </c>
       <c r="S2" s="27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="T2" s="27" t="s">
         <v>25</v>
@@ -2950,28 +2950,28 @@
       </c>
     </row>
     <row r="63" spans="1:21">
-      <c r="I63" s="61" t="s">
-        <v>129</v>
-      </c>
-      <c r="J63" s="61"/>
-      <c r="K63" s="61"/>
-      <c r="L63" s="61"/>
+      <c r="I63" s="60" t="s">
+        <v>128</v>
+      </c>
+      <c r="J63" s="60"/>
+      <c r="K63" s="60"/>
+      <c r="L63" s="60"/>
     </row>
     <row r="64" spans="1:21">
       <c r="I64" s="38" t="s">
+        <v>129</v>
+      </c>
+      <c r="J64" s="38" t="s">
         <v>130</v>
       </c>
-      <c r="J64" s="38" t="s">
+      <c r="K64" s="38" t="s">
         <v>131</v>
       </c>
-      <c r="K64" s="38" t="s">
-        <v>132</v>
-      </c>
       <c r="L64" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="M64" s="41" t="s">
         <v>146</v>
-      </c>
-      <c r="M64" s="41" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="65" spans="9:15" ht="15.6">
@@ -2982,10 +2982,10 @@
         <v>0</v>
       </c>
       <c r="K65" s="39" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L65" s="39" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M65">
         <f>COUNTIF($L$3:$L$52,L65)</f>
@@ -3004,10 +3004,10 @@
         <v>1</v>
       </c>
       <c r="K66" s="39" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L66" s="39" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M66">
         <f t="shared" ref="M66:M71" si="4">COUNTIF($L$3:$L$52,L66)</f>
@@ -3026,10 +3026,10 @@
         <v>2</v>
       </c>
       <c r="K67" s="39" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L67" s="39" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="M67">
         <f>COUNTIF($L$3:$L$52,L67)</f>
@@ -3048,10 +3048,10 @@
         <v>2.5</v>
       </c>
       <c r="K68" s="40" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L68" s="39" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M68">
         <f t="shared" si="4"/>
@@ -3074,10 +3074,10 @@
         <v>3</v>
       </c>
       <c r="K69" s="40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L69" s="39" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="M69">
         <f t="shared" si="4"/>
@@ -3100,10 +3100,10 @@
         <v>3.5</v>
       </c>
       <c r="K70" s="40" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L70" s="39" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="M70">
         <f t="shared" si="4"/>
@@ -3122,10 +3122,10 @@
         <v>4</v>
       </c>
       <c r="K71" s="40" t="s">
+        <v>137</v>
+      </c>
+      <c r="L71" s="39" t="s">
         <v>138</v>
-      </c>
-      <c r="L71" s="39" t="s">
-        <v>139</v>
       </c>
       <c r="M71">
         <f t="shared" si="4"/>
@@ -3176,20 +3176,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="56" customFormat="1" ht="39.75" customHeight="1">
-      <c r="A1" s="59" t="s">
-        <v>148</v>
-      </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
+      <c r="A1" s="61" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
     </row>
     <row r="2" spans="1:5" ht="35.85" customHeight="1">
       <c r="A2" s="44" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C2" s="45" t="s">
         <v>1</v>
@@ -3206,14 +3206,14 @@
         <v>1</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C3" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" s="49"/>
       <c r="E3" s="50" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="31.5" customHeight="1">
@@ -3221,14 +3221,14 @@
         <v>2</v>
       </c>
       <c r="B4" s="48" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C4" s="48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D4" s="49"/>
       <c r="E4" s="50" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="31.5" customHeight="1">
@@ -3236,14 +3236,14 @@
         <v>3</v>
       </c>
       <c r="B5" s="48" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D5" s="49"/>
       <c r="E5" s="50" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="31.5" customHeight="1">
@@ -3251,14 +3251,14 @@
         <v>4</v>
       </c>
       <c r="B6" s="48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C6" s="48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D6" s="49"/>
       <c r="E6" s="50" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="31.5" customHeight="1">
@@ -3266,14 +3266,14 @@
         <v>5</v>
       </c>
       <c r="B7" s="48" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C7" s="48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D7" s="49"/>
       <c r="E7" s="50" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="31.5" customHeight="1">
@@ -3281,14 +3281,14 @@
         <v>6</v>
       </c>
       <c r="B8" s="48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C8" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8" s="49"/>
       <c r="E8" s="50" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="31.5" customHeight="1">
@@ -3296,14 +3296,14 @@
         <v>7</v>
       </c>
       <c r="B9" s="48" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C9" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D9" s="49"/>
       <c r="E9" s="50" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="31.5" customHeight="1">
@@ -3311,14 +3311,14 @@
         <v>8</v>
       </c>
       <c r="B10" s="48" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C10" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D10" s="49"/>
       <c r="E10" s="50" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="31.5" customHeight="1">
@@ -3326,14 +3326,14 @@
         <v>9</v>
       </c>
       <c r="B11" s="48" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C11" s="48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D11" s="49"/>
       <c r="E11" s="50" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="31.5" customHeight="1">
@@ -3341,14 +3341,14 @@
         <v>10</v>
       </c>
       <c r="B12" s="48" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C12" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D12" s="49"/>
       <c r="E12" s="50" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="31.5" customHeight="1">
@@ -3356,14 +3356,14 @@
         <v>11</v>
       </c>
       <c r="B13" s="48" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D13" s="49"/>
       <c r="E13" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="31.5" customHeight="1">
@@ -3371,14 +3371,14 @@
         <v>12</v>
       </c>
       <c r="B14" s="48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C14" s="48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D14" s="49"/>
       <c r="E14" s="50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="31.5" customHeight="1">
@@ -3386,14 +3386,14 @@
         <v>13</v>
       </c>
       <c r="B15" s="48" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C15" s="48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D15" s="49"/>
       <c r="E15" s="50" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="31.5" customHeight="1">
@@ -3401,14 +3401,14 @@
         <v>14</v>
       </c>
       <c r="B16" s="48" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D16" s="49"/>
       <c r="E16" s="50" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="31.5" customHeight="1">
@@ -3416,14 +3416,14 @@
         <v>15</v>
       </c>
       <c r="B17" s="48" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C17" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D17" s="49"/>
       <c r="E17" s="50" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="31.5" customHeight="1">
@@ -3431,14 +3431,14 @@
         <v>16</v>
       </c>
       <c r="B18" s="48" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" s="49"/>
       <c r="E18" s="50" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="31.5" customHeight="1">
@@ -3446,14 +3446,14 @@
         <v>17</v>
       </c>
       <c r="B19" s="48" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C19" s="48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" s="49"/>
       <c r="E19" s="50" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="31.5" customHeight="1">
@@ -3461,14 +3461,14 @@
         <v>18</v>
       </c>
       <c r="B20" s="48" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C20" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D20" s="49"/>
       <c r="E20" s="50" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="31.5" customHeight="1">
@@ -3476,14 +3476,14 @@
         <v>19</v>
       </c>
       <c r="B21" s="48" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C21" s="48" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D21" s="49"/>
       <c r="E21" s="50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="31.5" customHeight="1">
@@ -3491,14 +3491,14 @@
         <v>20</v>
       </c>
       <c r="B22" s="48" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D22" s="49"/>
       <c r="E22" s="50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="31.5" customHeight="1">
@@ -3506,14 +3506,14 @@
         <v>21</v>
       </c>
       <c r="B23" s="48" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C23" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D23" s="49"/>
       <c r="E23" s="50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="31.5" customHeight="1">
@@ -3521,14 +3521,14 @@
         <v>22</v>
       </c>
       <c r="B24" s="48" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C24" s="48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D24" s="49"/>
       <c r="E24" s="50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="31.5" customHeight="1">
@@ -3536,14 +3536,14 @@
         <v>23</v>
       </c>
       <c r="B25" s="48" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D25" s="49"/>
       <c r="E25" s="50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="31.5" customHeight="1">
@@ -3551,14 +3551,14 @@
         <v>24</v>
       </c>
       <c r="B26" s="48" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C26" s="48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D26" s="49"/>
       <c r="E26" s="50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="31.5" customHeight="1">
@@ -3566,14 +3566,14 @@
         <v>25</v>
       </c>
       <c r="B27" s="48" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C27" s="48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D27" s="49"/>
       <c r="E27" s="50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="31.5" customHeight="1">
@@ -3581,14 +3581,14 @@
         <v>26</v>
       </c>
       <c r="B28" s="48" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C28" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D28" s="49"/>
       <c r="E28" s="50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="31.5" customHeight="1">
@@ -3596,14 +3596,14 @@
         <v>27</v>
       </c>
       <c r="B29" s="48" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C29" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D29" s="49"/>
       <c r="E29" s="50" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="31.5" customHeight="1">
@@ -3611,14 +3611,14 @@
         <v>28</v>
       </c>
       <c r="B30" s="48" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C30" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D30" s="49"/>
       <c r="E30" s="50" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="31.5" customHeight="1">
@@ -3626,14 +3626,14 @@
         <v>29</v>
       </c>
       <c r="B31" s="48" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C31" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D31" s="49"/>
       <c r="E31" s="50" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="31.5" customHeight="1">
@@ -3641,14 +3641,14 @@
         <v>30</v>
       </c>
       <c r="B32" s="48" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C32" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D32" s="49"/>
       <c r="E32" s="50" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="31.5" customHeight="1">
@@ -3656,10 +3656,10 @@
         <v>31</v>
       </c>
       <c r="B33" s="48" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C33" s="48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D33" s="49"/>
       <c r="E33" s="50" t="s">
@@ -3671,10 +3671,10 @@
         <v>32</v>
       </c>
       <c r="B34" s="48" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C34" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D34" s="49"/>
       <c r="E34" s="50" t="s">
@@ -3686,10 +3686,10 @@
         <v>33</v>
       </c>
       <c r="B35" s="48" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C35" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D35" s="50"/>
       <c r="E35" s="50" t="s">
@@ -3701,14 +3701,14 @@
         <v>34</v>
       </c>
       <c r="B36" s="48" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C36" s="48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D36" s="49"/>
       <c r="E36" s="50" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="31.5" customHeight="1">
@@ -3716,14 +3716,14 @@
         <v>35</v>
       </c>
       <c r="B37" s="48" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C37" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D37" s="49"/>
       <c r="E37" s="50" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="31.5" customHeight="1">
@@ -3731,10 +3731,10 @@
         <v>36</v>
       </c>
       <c r="B38" s="48" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C38" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D38" s="49"/>
       <c r="E38" s="50" t="s">
@@ -3746,10 +3746,10 @@
         <v>37</v>
       </c>
       <c r="B39" s="48" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C39" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D39" s="49"/>
       <c r="E39" s="50" t="s">
@@ -3761,10 +3761,10 @@
         <v>38</v>
       </c>
       <c r="B40" s="48" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C40" s="48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D40" s="49"/>
       <c r="E40" s="50" t="s">
@@ -3776,10 +3776,10 @@
         <v>39</v>
       </c>
       <c r="B41" s="48" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C41" s="48" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D41" s="49"/>
       <c r="E41" s="50" t="s">
@@ -3791,10 +3791,10 @@
         <v>40</v>
       </c>
       <c r="B42" s="48" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C42" s="48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D42" s="49"/>
       <c r="E42" s="50" t="s">
@@ -3806,10 +3806,10 @@
         <v>41</v>
       </c>
       <c r="B43" s="48" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C43" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D43" s="49"/>
       <c r="E43" s="50" t="s">
@@ -3821,10 +3821,10 @@
         <v>42</v>
       </c>
       <c r="B44" s="52" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C44" s="52" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D44" s="53"/>
       <c r="E44" s="54" t="s">
@@ -3836,10 +3836,10 @@
         <v>43</v>
       </c>
       <c r="B45" s="48" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C45" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D45" s="49"/>
       <c r="E45" s="50" t="s">
@@ -3851,10 +3851,10 @@
         <v>44</v>
       </c>
       <c r="B46" s="48" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C46" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D46" s="49"/>
       <c r="E46" s="50" t="s">
@@ -3866,14 +3866,14 @@
         <v>45</v>
       </c>
       <c r="B47" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C47" s="48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D47" s="49"/>
       <c r="E47" s="50" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="31.5" customHeight="1">
@@ -3881,14 +3881,14 @@
         <v>46</v>
       </c>
       <c r="B48" s="48" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C48" s="48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D48" s="49"/>
       <c r="E48" s="55" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="31.5" customHeight="1">
@@ -3896,14 +3896,14 @@
         <v>47</v>
       </c>
       <c r="B49" s="48" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C49" s="48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D49" s="49"/>
       <c r="E49" s="55" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="31.5" customHeight="1">
@@ -3911,14 +3911,14 @@
         <v>48</v>
       </c>
       <c r="B50" s="48" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C50" s="48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D50" s="49"/>
       <c r="E50" s="55" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="31.5" customHeight="1">
@@ -3926,14 +3926,14 @@
         <v>49</v>
       </c>
       <c r="B51" s="48" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C51" s="48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D51" s="49"/>
       <c r="E51" s="55" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="31.5" customHeight="1">
@@ -3941,14 +3941,14 @@
         <v>50</v>
       </c>
       <c r="B52" s="48" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C52" s="48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D52" s="49"/>
       <c r="E52" s="50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -4021,10 +4021,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D3" s="10">
         <v>10</v>
@@ -4039,17 +4039,17 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D4" s="10">
         <v>6</v>
       </c>
       <c r="E4" s="20"/>
       <c r="F4" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="33.6">
@@ -4060,7 +4060,7 @@
         <v>20</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D5" s="10">
         <v>3</v>
@@ -4075,17 +4075,17 @@
         <v>5</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D6" s="10">
         <v>4</v>
       </c>
       <c r="E6" s="19"/>
       <c r="F6" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -4093,19 +4093,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D7" s="10">
         <v>2</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -4113,19 +4113,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="D8" s="10">
         <v>1</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4133,17 +4133,17 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>39</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>40</v>
       </c>
       <c r="D9" s="10">
         <v>1</v>
       </c>
       <c r="E9" s="19"/>
       <c r="F9" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -4151,17 +4151,17 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>47</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>48</v>
       </c>
       <c r="D10" s="10">
         <v>4</v>
       </c>
       <c r="E10" s="19"/>
       <c r="F10" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -4169,7 +4169,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="10">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="E11" s="19"/>
       <c r="F11" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="21.75" customHeight="1">
@@ -4185,10 +4185,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" s="10">
         <v>3</v>
@@ -4203,10 +4203,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="D13" s="10">
         <v>1</v>
@@ -4219,10 +4219,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="26" t="s">
         <v>55</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>56</v>
       </c>
       <c r="D14" s="10">
         <v>2</v>
@@ -4235,10 +4235,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D15" s="10">
         <v>1</v>
@@ -4251,17 +4251,17 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" s="10">
         <v>1</v>
       </c>
       <c r="E16" s="19"/>
       <c r="F16" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G16" s="9"/>
     </row>

--- a/backend/InternLink/InternLink.API/Templates/InternshipExportTemplate.xlsx
+++ b/backend/InternLink/InternLink.API/Templates/InternshipExportTemplate.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\InternLink\backend\InternLink\InternLink.API\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1969052-3C90-4C2E-B0DE-45C0DD77BC37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F245EE65-8282-461F-BF56-3C92DE9CBEF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="DANH SÁCH (2)" sheetId="4" r:id="rId1"/>
+    <sheet name="DANH SÁCH " sheetId="4" r:id="rId1"/>
     <sheet name="DATABASE" sheetId="2" r:id="rId2"/>
     <sheet name="TÊN CÔNG TY" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DANH SÁCH (2)'!$A$2:$U$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DANH SÁCH '!$A$2:$U$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DATABASE!$E$1:$E$52</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="49">
   <si>
     <t>STT</t>
   </si>
@@ -57,12 +57,6 @@
  THỰC TẬP</t>
   </si>
   <si>
-    <t xml:space="preserve">292/33/10 Bình Lợi phường 13 quận Bình Thạnh </t>
-  </si>
-  <si>
-    <t>Lê Nguyên Vỹ</t>
-  </si>
-  <si>
     <t>Tên Công Ty</t>
   </si>
   <si>
@@ -75,12 +69,6 @@
     <t>Liên Hệ</t>
   </si>
   <si>
-    <t>Công ty TNHH thiết kế và quảng cáo Tivatech</t>
-  </si>
-  <si>
-    <t>Chị Hằng</t>
-  </si>
-  <si>
     <t>GHI CHÚ</t>
   </si>
   <si>
@@ -102,17 +90,6 @@
     <t>TUẦN 5</t>
   </si>
   <si>
-    <t>Công ty TNHH Giải Pháp Tiên Khanh</t>
-  </si>
-  <si>
-    <t>Anh Tiên
-0909 22 10 13</t>
-  </si>
-  <si>
-    <t>Anh Cường
-093 797 56 78</t>
-  </si>
-  <si>
     <t>Điểm tham gia</t>
   </si>
   <si>
@@ -122,292 +99,13 @@
     <t>NỘP BC</t>
   </si>
   <si>
-    <t>C23A.TH2</t>
-  </si>
-  <si>
-    <t>C23A.TH1</t>
-  </si>
-  <si>
-    <t>C22A.TH</t>
-  </si>
-  <si>
-    <t>Công ty TNHH Giải pháp Công nghệ SLK</t>
-  </si>
-  <si>
-    <t>Quốc Tùng C19</t>
-  </si>
-  <si>
     <t>HỌ</t>
   </si>
   <si>
     <t>TÊN</t>
   </si>
   <si>
-    <t>351B Nơ Trang Long, Phường 13, Quận Bình Thạnh</t>
-  </si>
-  <si>
-    <t>Số 699 Nguyễn Kiệm, Phường Hạnh Thông, Thành phố Hồ Chí Minh</t>
-  </si>
-  <si>
-    <t>Lâm Sĩ Thành</t>
-  </si>
-  <si>
-    <t>Công Ty TNHH Trường Thịnh Group</t>
-  </si>
-  <si>
-    <t>881 Phan Văn Trị, Phường 1, Gò Vấp, TP.HCM</t>
-  </si>
-  <si>
-    <t>Công ty TNHH Di4L</t>
-  </si>
-  <si>
-    <t>23 Phạm Thị Kỳ, Phú Xuân, Nhà Bè, TP HCM</t>
-  </si>
-  <si>
-    <t>Trần Xuân Bình</t>
-  </si>
-  <si>
-    <t>Nguyễn Phúc Hưng</t>
-  </si>
-  <si>
-    <t>0865207989</t>
-  </si>
-  <si>
-    <t>0707096625</t>
-  </si>
-  <si>
-    <t>Công ty TNHH Dịch vụ công nghệ LIS</t>
-  </si>
-  <si>
-    <t>Thông</t>
-  </si>
-  <si>
-    <t>Công ty CP Truyền thông Bright Star</t>
-  </si>
-  <si>
-    <t>4/6b Văn Chung, Phường 13, Quận Tân Bình, Thành phố Hồ Chí Minh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anh Nghĩa </t>
-  </si>
-  <si>
-    <t>Thu</t>
-  </si>
-  <si>
-    <t>Công ty TNHH TM DV Trí Lực Việt</t>
-  </si>
-  <si>
-    <t>Công ty cổ phần EZTEC</t>
-  </si>
-  <si>
-    <t>Công ty Cổ phần Công nghệ RADA360</t>
-  </si>
-  <si>
-    <t>114 Đường số 2, Cư xá Đô Thành, Phường Bàn Cờ</t>
-  </si>
-  <si>
-    <t>Công ty TNHH Tư Vấn &amp; Đào Tạo Đại Dương</t>
-  </si>
-  <si>
-    <t>25 Đ. Số 23, Linh Chiểu, Thủ Đức, Hồ Chí Minh</t>
-  </si>
-  <si>
-    <t>Công Ty TNHH công nghệ phần mềm Nasani</t>
-  </si>
-  <si>
-    <t>Tầng 5, Tòa Nhà TTM Building, Số 309 Bạch Đằng</t>
-  </si>
-  <si>
-    <t>PHẠM THÀNH CÔNG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cty TNHH Công nghệ kỹ thuật  Ô TÔ TCT </t>
-  </si>
-  <si>
-    <t>Nguyễn Phi Long</t>
-  </si>
-  <si>
-    <t>Huỳnh Văn Trương</t>
-  </si>
-  <si>
-    <t>Nguyễn Quốc Đạt</t>
-  </si>
-  <si>
-    <t>Hà Tuấn Anh</t>
-  </si>
-  <si>
     <t>HỌ TÊN</t>
-  </si>
-  <si>
-    <t>Phạm Thành Đạt</t>
-  </si>
-  <si>
-    <t>Phạm Huỳnh Anh</t>
-  </si>
-  <si>
-    <t>Trịnh Gia Hào</t>
-  </si>
-  <si>
-    <t>Nguyễn Lê Minh Khôi</t>
-  </si>
-  <si>
-    <t>Nguyễn Hữu Luân</t>
-  </si>
-  <si>
-    <t>Trần Minh Tâm</t>
-  </si>
-  <si>
-    <t>Nguyễn Hiền Vy</t>
-  </si>
-  <si>
-    <t>Trần Thanh Tuấn</t>
-  </si>
-  <si>
-    <t>Lê Quang Bảo</t>
-  </si>
-  <si>
-    <t>Trần Nguyễn Thành Đạt</t>
-  </si>
-  <si>
-    <t>Lê Văn Hoàng Hiếu</t>
-  </si>
-  <si>
-    <t>Dương Tự Lực</t>
-  </si>
-  <si>
-    <t>Liêu Hoàng Phúc</t>
-  </si>
-  <si>
-    <t>Lê Văn Thắng</t>
-  </si>
-  <si>
-    <t>Phạm Duy Văn</t>
-  </si>
-  <si>
-    <t>Nguyễn Thanh An</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Chung</t>
-  </si>
-  <si>
-    <t>Võ Quốc Đạt</t>
-  </si>
-  <si>
-    <t>Nguyễn Tuấn Kiệt</t>
-  </si>
-  <si>
-    <t>Nguyễn Văn Nam</t>
-  </si>
-  <si>
-    <t>Thành Xuân Phúc</t>
-  </si>
-  <si>
-    <t>Phạm Đức Trọng</t>
-  </si>
-  <si>
-    <t>Lê Việt</t>
-  </si>
-  <si>
-    <t>Vũ Xuân An</t>
-  </si>
-  <si>
-    <t>Trần Nhật Cường</t>
-  </si>
-  <si>
-    <t>Đặng Khánh Duy</t>
-  </si>
-  <si>
-    <t>Ngô Trung Hiếu Kiên</t>
-  </si>
-  <si>
-    <t>Nguyễn Ngọc Linh</t>
-  </si>
-  <si>
-    <t>Võ Minh Nam</t>
-  </si>
-  <si>
-    <t>Nguyễn Minh Quân</t>
-  </si>
-  <si>
-    <t>Nguyễn Đoàn Thanh Vũ</t>
-  </si>
-  <si>
-    <t>Nguyễn Huỳnh Hoàng Anh</t>
-  </si>
-  <si>
-    <t>Phùng Thị Ngọc Hân</t>
-  </si>
-  <si>
-    <t>Võ Lê Tường Khánh</t>
-  </si>
-  <si>
-    <t>Lê Minh Luân</t>
-  </si>
-  <si>
-    <t>Trần Quang Nhã</t>
-  </si>
-  <si>
-    <t>Chhom Ri</t>
-  </si>
-  <si>
-    <t>Nguyễn Thanh Tú</t>
-  </si>
-  <si>
-    <t>Lê Văn Thành Đạt</t>
-  </si>
-  <si>
-    <t>Nguyễn Phước Duy</t>
-  </si>
-  <si>
-    <t>Bùi Thiên Huy</t>
-  </si>
-  <si>
-    <t>K Pă Y San Hy</t>
-  </si>
-  <si>
-    <t>Lê Thế Nguyên</t>
-  </si>
-  <si>
-    <t>Nguyễn Hoàng Phú</t>
-  </si>
-  <si>
-    <t>Vũ Minh Quân</t>
-  </si>
-  <si>
-    <t>Nguyễn Xuân Trường</t>
-  </si>
-  <si>
-    <t>Công ty TNHH SUN SMART</t>
-  </si>
-  <si>
-    <t>Công ty TNHH Điện Tử - Viễn thông Gia Ngọc Việt</t>
-  </si>
-  <si>
-    <t>Công ty cổ phần Truyền thông Bright Star</t>
-  </si>
-  <si>
-    <t>Công ty cổ phần truyền thông Bright Star</t>
-  </si>
-  <si>
-    <t>24/10 Đường 31, Bình Trưng Tây</t>
-  </si>
-  <si>
-    <t>Số 17 Đường 34, khu phố 5, Phường An Phú</t>
-  </si>
-  <si>
-    <t>939 Phạm Văn Bạch, Phường 12, quận Gò Vấp</t>
-  </si>
-  <si>
-    <t>5 Giang Văn Minh, An phú, HCM</t>
-  </si>
-  <si>
-    <t>Lầu 1 Tòa nhà Saigon ICT, Lô 46 CV Phần Mềm Quang Trung, Phường Trung Mỹ Tây</t>
-  </si>
-  <si>
-    <t>Công ty TNHH Điện tử viễn thông Gia Ngọc Việt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Công ty TNHH Công nghệ kỹ thuật ÔTÔ TCT </t>
   </si>
   <si>
     <t>TUẦN 6</t>
@@ -1261,7 +959,7 @@
   <sheetData>
     <row r="1" spans="1:21" s="3" customFormat="1" ht="39.75" customHeight="1">
       <c r="A1" s="59" t="s">
-        <v>148</v>
+        <v>48</v>
       </c>
       <c r="B1" s="59"/>
       <c r="C1" s="59"/>
@@ -1289,10 +987,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>1</v>
@@ -1304,49 +1002,49 @@
         <v>4</v>
       </c>
       <c r="G2" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="P2" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="J2" s="35" t="s">
-        <v>124</v>
-      </c>
-      <c r="K2" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="L2" s="37" t="s">
-        <v>127</v>
-      </c>
-      <c r="M2" s="29" t="s">
+      <c r="Q2" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="27" t="s">
+      <c r="R2" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="P2" s="27" t="s">
+      <c r="S2" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="T2" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="U2" s="10" t="s">
         <v>17</v>
-      </c>
-      <c r="Q2" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="R2" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="S2" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="T2" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="U2" s="10" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="24.75" customHeight="1">
@@ -2951,7 +2649,7 @@
     </row>
     <row r="63" spans="1:21">
       <c r="I63" s="60" t="s">
-        <v>128</v>
+        <v>28</v>
       </c>
       <c r="J63" s="60"/>
       <c r="K63" s="60"/>
@@ -2959,19 +2657,19 @@
     </row>
     <row r="64" spans="1:21">
       <c r="I64" s="38" t="s">
-        <v>129</v>
+        <v>29</v>
       </c>
       <c r="J64" s="38" t="s">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="K64" s="38" t="s">
-        <v>131</v>
+        <v>31</v>
       </c>
       <c r="L64" s="38" t="s">
-        <v>145</v>
+        <v>45</v>
       </c>
       <c r="M64" s="41" t="s">
-        <v>146</v>
+        <v>46</v>
       </c>
     </row>
     <row r="65" spans="9:15" ht="15.6">
@@ -2982,10 +2680,10 @@
         <v>0</v>
       </c>
       <c r="K65" s="39" t="s">
-        <v>132</v>
+        <v>32</v>
       </c>
       <c r="L65" s="39" t="s">
-        <v>144</v>
+        <v>44</v>
       </c>
       <c r="M65">
         <f>COUNTIF($L$3:$L$52,L65)</f>
@@ -3004,10 +2702,10 @@
         <v>1</v>
       </c>
       <c r="K66" s="39" t="s">
-        <v>133</v>
+        <v>33</v>
       </c>
       <c r="L66" s="39" t="s">
-        <v>143</v>
+        <v>43</v>
       </c>
       <c r="M66">
         <f t="shared" ref="M66:M71" si="4">COUNTIF($L$3:$L$52,L66)</f>
@@ -3026,10 +2724,10 @@
         <v>2</v>
       </c>
       <c r="K67" s="39" t="s">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="L67" s="39" t="s">
-        <v>142</v>
+        <v>42</v>
       </c>
       <c r="M67">
         <f>COUNTIF($L$3:$L$52,L67)</f>
@@ -3048,10 +2746,10 @@
         <v>2.5</v>
       </c>
       <c r="K68" s="40" t="s">
-        <v>134</v>
+        <v>34</v>
       </c>
       <c r="L68" s="39" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="M68">
         <f t="shared" si="4"/>
@@ -3074,10 +2772,10 @@
         <v>3</v>
       </c>
       <c r="K69" s="40" t="s">
-        <v>135</v>
+        <v>35</v>
       </c>
       <c r="L69" s="39" t="s">
-        <v>140</v>
+        <v>40</v>
       </c>
       <c r="M69">
         <f t="shared" si="4"/>
@@ -3100,10 +2798,10 @@
         <v>3.5</v>
       </c>
       <c r="K70" s="40" t="s">
-        <v>136</v>
+        <v>36</v>
       </c>
       <c r="L70" s="39" t="s">
-        <v>139</v>
+        <v>39</v>
       </c>
       <c r="M70">
         <f t="shared" si="4"/>
@@ -3122,10 +2820,10 @@
         <v>4</v>
       </c>
       <c r="K71" s="40" t="s">
-        <v>137</v>
+        <v>37</v>
       </c>
       <c r="L71" s="39" t="s">
-        <v>138</v>
+        <v>38</v>
       </c>
       <c r="M71">
         <f t="shared" si="4"/>
@@ -3177,7 +2875,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="56" customFormat="1" ht="39.75" customHeight="1">
       <c r="A1" s="61" t="s">
-        <v>147</v>
+        <v>47</v>
       </c>
       <c r="B1" s="61"/>
       <c r="C1" s="61"/>
@@ -3189,7 +2887,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="C2" s="45" t="s">
         <v>1</v>
@@ -3205,751 +2903,451 @@
       <c r="A3" s="47">
         <v>1</v>
       </c>
-      <c r="B3" s="48" t="s">
-        <v>79</v>
-      </c>
-      <c r="C3" s="48" t="s">
-        <v>26</v>
-      </c>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
       <c r="D3" s="49"/>
-      <c r="E3" s="50" t="s">
-        <v>52</v>
-      </c>
+      <c r="E3" s="50"/>
     </row>
     <row r="4" spans="1:5" ht="31.5" customHeight="1">
       <c r="A4" s="47">
         <v>2</v>
       </c>
-      <c r="B4" s="48" t="s">
-        <v>103</v>
-      </c>
-      <c r="C4" s="48" t="s">
-        <v>27</v>
-      </c>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
       <c r="D4" s="49"/>
-      <c r="E4" s="50" t="s">
-        <v>51</v>
-      </c>
+      <c r="E4" s="50"/>
     </row>
     <row r="5" spans="1:5" ht="31.5" customHeight="1">
       <c r="A5" s="47">
         <v>3</v>
       </c>
-      <c r="B5" s="48" t="s">
-        <v>95</v>
-      </c>
-      <c r="C5" s="48" t="s">
-        <v>26</v>
-      </c>
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
       <c r="D5" s="49"/>
-      <c r="E5" s="50" t="s">
-        <v>51</v>
-      </c>
+      <c r="E5" s="50"/>
     </row>
     <row r="6" spans="1:5" ht="31.5" customHeight="1">
       <c r="A6" s="47">
         <v>4</v>
       </c>
-      <c r="B6" s="48" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" s="48" t="s">
-        <v>27</v>
-      </c>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
       <c r="D6" s="49"/>
-      <c r="E6" s="50" t="s">
-        <v>51</v>
-      </c>
+      <c r="E6" s="50"/>
     </row>
     <row r="7" spans="1:5" ht="31.5" customHeight="1">
       <c r="A7" s="47">
         <v>5</v>
       </c>
-      <c r="B7" s="48" t="s">
-        <v>105</v>
-      </c>
-      <c r="C7" s="48" t="s">
-        <v>27</v>
-      </c>
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
       <c r="D7" s="49"/>
-      <c r="E7" s="50" t="s">
-        <v>114</v>
-      </c>
+      <c r="E7" s="50"/>
     </row>
     <row r="8" spans="1:5" ht="31.5" customHeight="1">
       <c r="A8" s="47">
         <v>6</v>
       </c>
-      <c r="B8" s="48" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" s="48" t="s">
-        <v>26</v>
-      </c>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
       <c r="D8" s="49"/>
-      <c r="E8" s="50" t="s">
-        <v>114</v>
-      </c>
+      <c r="E8" s="50"/>
     </row>
     <row r="9" spans="1:5" ht="31.5" customHeight="1">
       <c r="A9" s="47">
         <v>7</v>
       </c>
-      <c r="B9" s="48" t="s">
-        <v>104</v>
-      </c>
-      <c r="C9" s="48" t="s">
-        <v>26</v>
-      </c>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
       <c r="D9" s="49"/>
-      <c r="E9" s="50" t="s">
-        <v>114</v>
-      </c>
+      <c r="E9" s="50"/>
     </row>
     <row r="10" spans="1:5" ht="31.5" customHeight="1">
       <c r="A10" s="47">
         <v>8</v>
       </c>
-      <c r="B10" s="48" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" s="48" t="s">
-        <v>26</v>
-      </c>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
       <c r="D10" s="49"/>
-      <c r="E10" s="50" t="s">
-        <v>113</v>
-      </c>
+      <c r="E10" s="50"/>
     </row>
     <row r="11" spans="1:5" ht="31.5" customHeight="1">
       <c r="A11" s="47">
         <v>9</v>
       </c>
-      <c r="B11" s="48" t="s">
-        <v>88</v>
-      </c>
-      <c r="C11" s="48" t="s">
-        <v>27</v>
-      </c>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
       <c r="D11" s="49"/>
-      <c r="E11" s="50" t="s">
-        <v>114</v>
-      </c>
+      <c r="E11" s="50"/>
     </row>
     <row r="12" spans="1:5" ht="31.5" customHeight="1">
       <c r="A12" s="47">
         <v>10</v>
       </c>
-      <c r="B12" s="48" t="s">
-        <v>92</v>
-      </c>
-      <c r="C12" s="48" t="s">
-        <v>26</v>
-      </c>
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
       <c r="D12" s="49"/>
-      <c r="E12" s="50" t="s">
-        <v>114</v>
-      </c>
+      <c r="E12" s="50"/>
     </row>
     <row r="13" spans="1:5" ht="31.5" customHeight="1">
       <c r="A13" s="47">
         <v>11</v>
       </c>
-      <c r="B13" s="48" t="s">
-        <v>96</v>
-      </c>
-      <c r="C13" s="48" t="s">
-        <v>26</v>
-      </c>
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
       <c r="D13" s="49"/>
-      <c r="E13" s="48" t="s">
-        <v>56</v>
-      </c>
+      <c r="E13" s="48"/>
     </row>
     <row r="14" spans="1:5" ht="31.5" customHeight="1">
       <c r="A14" s="47">
         <v>12</v>
       </c>
-      <c r="B14" s="48" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" s="48" t="s">
-        <v>27</v>
-      </c>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
       <c r="D14" s="49"/>
-      <c r="E14" s="50" t="s">
-        <v>38</v>
-      </c>
+      <c r="E14" s="50"/>
     </row>
     <row r="15" spans="1:5" ht="31.5" customHeight="1">
       <c r="A15" s="47">
         <v>13</v>
       </c>
-      <c r="B15" s="48" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" s="48" t="s">
-        <v>27</v>
-      </c>
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
       <c r="D15" s="49"/>
-      <c r="E15" s="50" t="s">
-        <v>44</v>
-      </c>
+      <c r="E15" s="50"/>
     </row>
     <row r="16" spans="1:5" ht="31.5" customHeight="1">
       <c r="A16" s="47">
         <v>14</v>
       </c>
-      <c r="B16" s="48" t="s">
-        <v>107</v>
-      </c>
-      <c r="C16" s="48" t="s">
-        <v>26</v>
-      </c>
+      <c r="B16" s="48"/>
+      <c r="C16" s="48"/>
       <c r="D16" s="49"/>
-      <c r="E16" s="50" t="s">
-        <v>44</v>
-      </c>
+      <c r="E16" s="50"/>
     </row>
     <row r="17" spans="1:5" ht="31.5" customHeight="1">
       <c r="A17" s="47">
         <v>15</v>
       </c>
-      <c r="B17" s="48" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="48" t="s">
-        <v>26</v>
-      </c>
+      <c r="B17" s="48"/>
+      <c r="C17" s="48"/>
       <c r="D17" s="49"/>
-      <c r="E17" s="50" t="s">
-        <v>44</v>
-      </c>
+      <c r="E17" s="50"/>
     </row>
     <row r="18" spans="1:5" ht="31.5" customHeight="1">
       <c r="A18" s="47">
         <v>16</v>
       </c>
-      <c r="B18" s="48" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" s="48" t="s">
-        <v>26</v>
-      </c>
+      <c r="B18" s="48"/>
+      <c r="C18" s="48"/>
       <c r="D18" s="49"/>
-      <c r="E18" s="50" t="s">
-        <v>44</v>
-      </c>
+      <c r="E18" s="50"/>
     </row>
     <row r="19" spans="1:5" ht="31.5" customHeight="1">
       <c r="A19" s="47">
         <v>17</v>
       </c>
-      <c r="B19" s="48" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" s="48" t="s">
-        <v>27</v>
-      </c>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
       <c r="D19" s="49"/>
-      <c r="E19" s="50" t="s">
-        <v>44</v>
-      </c>
+      <c r="E19" s="50"/>
     </row>
     <row r="20" spans="1:5" ht="31.5" customHeight="1">
       <c r="A20" s="47">
         <v>18</v>
       </c>
-      <c r="B20" s="48" t="s">
-        <v>109</v>
-      </c>
-      <c r="C20" s="48" t="s">
-        <v>26</v>
-      </c>
+      <c r="B20" s="48"/>
+      <c r="C20" s="48"/>
       <c r="D20" s="49"/>
-      <c r="E20" s="50" t="s">
-        <v>44</v>
-      </c>
+      <c r="E20" s="50"/>
     </row>
     <row r="21" spans="1:5" ht="31.5" customHeight="1">
       <c r="A21" s="47">
         <v>19</v>
       </c>
-      <c r="B21" s="48" t="s">
-        <v>63</v>
-      </c>
-      <c r="C21" s="48" t="s">
-        <v>28</v>
-      </c>
+      <c r="B21" s="48"/>
+      <c r="C21" s="48"/>
       <c r="D21" s="49"/>
-      <c r="E21" s="50" t="s">
-        <v>112</v>
-      </c>
+      <c r="E21" s="50"/>
     </row>
     <row r="22" spans="1:5" ht="31.5" customHeight="1">
       <c r="A22" s="47">
         <v>20</v>
       </c>
-      <c r="B22" s="48" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" s="48" t="s">
-        <v>28</v>
-      </c>
+      <c r="B22" s="48"/>
+      <c r="C22" s="48"/>
       <c r="D22" s="49"/>
-      <c r="E22" s="50" t="s">
-        <v>112</v>
-      </c>
+      <c r="E22" s="50"/>
     </row>
     <row r="23" spans="1:5" ht="31.5" customHeight="1">
       <c r="A23" s="47">
         <v>21</v>
       </c>
-      <c r="B23" s="48" t="s">
-        <v>99</v>
-      </c>
-      <c r="C23" s="48" t="s">
-        <v>26</v>
-      </c>
+      <c r="B23" s="48"/>
+      <c r="C23" s="48"/>
       <c r="D23" s="49"/>
-      <c r="E23" s="50" t="s">
-        <v>112</v>
-      </c>
+      <c r="E23" s="50"/>
     </row>
     <row r="24" spans="1:5" ht="31.5" customHeight="1">
       <c r="A24" s="47">
         <v>22</v>
       </c>
-      <c r="B24" s="48" t="s">
-        <v>60</v>
-      </c>
-      <c r="C24" s="48" t="s">
-        <v>27</v>
-      </c>
+      <c r="B24" s="48"/>
+      <c r="C24" s="48"/>
       <c r="D24" s="49"/>
-      <c r="E24" s="50" t="s">
-        <v>112</v>
-      </c>
+      <c r="E24" s="50"/>
     </row>
     <row r="25" spans="1:5" ht="31.5" customHeight="1">
       <c r="A25" s="47">
         <v>23</v>
       </c>
-      <c r="B25" s="48" t="s">
-        <v>110</v>
-      </c>
-      <c r="C25" s="48" t="s">
-        <v>27</v>
-      </c>
+      <c r="B25" s="48"/>
+      <c r="C25" s="48"/>
       <c r="D25" s="49"/>
-      <c r="E25" s="50" t="s">
-        <v>112</v>
-      </c>
+      <c r="E25" s="50"/>
     </row>
     <row r="26" spans="1:5" ht="31.5" customHeight="1">
       <c r="A26" s="47">
         <v>24</v>
       </c>
-      <c r="B26" s="48" t="s">
-        <v>70</v>
-      </c>
-      <c r="C26" s="48" t="s">
-        <v>27</v>
-      </c>
+      <c r="B26" s="48"/>
+      <c r="C26" s="48"/>
       <c r="D26" s="49"/>
-      <c r="E26" s="50" t="s">
-        <v>112</v>
-      </c>
+      <c r="E26" s="50"/>
     </row>
     <row r="27" spans="1:5" ht="31.5" customHeight="1">
       <c r="A27" s="47">
         <v>25</v>
       </c>
-      <c r="B27" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="C27" s="48" t="s">
-        <v>27</v>
-      </c>
+      <c r="B27" s="48"/>
+      <c r="C27" s="48"/>
       <c r="D27" s="49"/>
-      <c r="E27" s="50" t="s">
-        <v>112</v>
-      </c>
+      <c r="E27" s="50"/>
     </row>
     <row r="28" spans="1:5" ht="31.5" customHeight="1">
       <c r="A28" s="47">
         <v>26</v>
       </c>
-      <c r="B28" s="48" t="s">
-        <v>100</v>
-      </c>
-      <c r="C28" s="48" t="s">
-        <v>26</v>
-      </c>
+      <c r="B28" s="48"/>
+      <c r="C28" s="48"/>
       <c r="D28" s="49"/>
-      <c r="E28" s="50" t="s">
-        <v>112</v>
-      </c>
+      <c r="E28" s="50"/>
     </row>
     <row r="29" spans="1:5" ht="31.5" customHeight="1">
       <c r="A29" s="47">
         <v>27</v>
       </c>
-      <c r="B29" s="48" t="s">
-        <v>75</v>
-      </c>
-      <c r="C29" s="48" t="s">
-        <v>26</v>
-      </c>
+      <c r="B29" s="48"/>
+      <c r="C29" s="48"/>
       <c r="D29" s="49"/>
-      <c r="E29" s="50" t="s">
-        <v>29</v>
-      </c>
+      <c r="E29" s="50"/>
     </row>
     <row r="30" spans="1:5" ht="31.5" customHeight="1">
       <c r="A30" s="47">
         <v>28</v>
       </c>
-      <c r="B30" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" s="48" t="s">
-        <v>26</v>
-      </c>
+      <c r="B30" s="48"/>
+      <c r="C30" s="48"/>
       <c r="D30" s="49"/>
-      <c r="E30" s="50" t="s">
-        <v>29</v>
-      </c>
+      <c r="E30" s="50"/>
     </row>
     <row r="31" spans="1:5" ht="31.5" customHeight="1">
       <c r="A31" s="47">
         <v>29</v>
       </c>
-      <c r="B31" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="C31" s="48" t="s">
-        <v>26</v>
-      </c>
+      <c r="B31" s="48"/>
+      <c r="C31" s="48"/>
       <c r="D31" s="49"/>
-      <c r="E31" s="50" t="s">
-        <v>29</v>
-      </c>
+      <c r="E31" s="50"/>
     </row>
     <row r="32" spans="1:5" ht="31.5" customHeight="1">
       <c r="A32" s="47">
         <v>30</v>
       </c>
-      <c r="B32" s="48" t="s">
-        <v>94</v>
-      </c>
-      <c r="C32" s="48" t="s">
-        <v>26</v>
-      </c>
+      <c r="B32" s="48"/>
+      <c r="C32" s="48"/>
       <c r="D32" s="49"/>
-      <c r="E32" s="50" t="s">
-        <v>29</v>
-      </c>
+      <c r="E32" s="50"/>
     </row>
     <row r="33" spans="1:5" ht="31.5" customHeight="1">
       <c r="A33" s="47">
         <v>31</v>
       </c>
-      <c r="B33" s="48" t="s">
-        <v>73</v>
-      </c>
-      <c r="C33" s="48" t="s">
-        <v>27</v>
-      </c>
+      <c r="B33" s="48"/>
+      <c r="C33" s="48"/>
       <c r="D33" s="49"/>
-      <c r="E33" s="50" t="s">
-        <v>20</v>
-      </c>
+      <c r="E33" s="50"/>
     </row>
     <row r="34" spans="1:5" ht="31.5" customHeight="1">
       <c r="A34" s="47">
         <v>32</v>
       </c>
-      <c r="B34" s="48" t="s">
-        <v>85</v>
-      </c>
-      <c r="C34" s="48" t="s">
-        <v>26</v>
-      </c>
+      <c r="B34" s="48"/>
+      <c r="C34" s="48"/>
       <c r="D34" s="49"/>
-      <c r="E34" s="50" t="s">
-        <v>20</v>
-      </c>
+      <c r="E34" s="50"/>
     </row>
     <row r="35" spans="1:5" ht="31.5" customHeight="1">
       <c r="A35" s="47">
         <v>33</v>
       </c>
-      <c r="B35" s="48" t="s">
-        <v>98</v>
-      </c>
-      <c r="C35" s="48" t="s">
-        <v>26</v>
-      </c>
+      <c r="B35" s="48"/>
+      <c r="C35" s="48"/>
       <c r="D35" s="50"/>
-      <c r="E35" s="50" t="s">
-        <v>20</v>
-      </c>
+      <c r="E35" s="50"/>
     </row>
     <row r="36" spans="1:5" ht="31.5" customHeight="1">
       <c r="A36" s="47">
         <v>34</v>
       </c>
-      <c r="B36" s="48" t="s">
-        <v>90</v>
-      </c>
-      <c r="C36" s="48" t="s">
-        <v>27</v>
-      </c>
+      <c r="B36" s="48"/>
+      <c r="C36" s="48"/>
       <c r="D36" s="49"/>
-      <c r="E36" s="50" t="s">
-        <v>111</v>
-      </c>
+      <c r="E36" s="50"/>
     </row>
     <row r="37" spans="1:5" ht="31.5" customHeight="1">
       <c r="A37" s="47">
         <v>35</v>
       </c>
-      <c r="B37" s="48" t="s">
-        <v>65</v>
-      </c>
-      <c r="C37" s="48" t="s">
-        <v>26</v>
-      </c>
+      <c r="B37" s="48"/>
+      <c r="C37" s="48"/>
       <c r="D37" s="49"/>
-      <c r="E37" s="50" t="s">
-        <v>111</v>
-      </c>
+      <c r="E37" s="50"/>
     </row>
     <row r="38" spans="1:5" ht="31.5" customHeight="1">
       <c r="A38" s="47">
         <v>36</v>
       </c>
-      <c r="B38" s="48" t="s">
-        <v>101</v>
-      </c>
-      <c r="C38" s="48" t="s">
-        <v>26</v>
-      </c>
+      <c r="B38" s="48"/>
+      <c r="C38" s="48"/>
       <c r="D38" s="49"/>
-      <c r="E38" s="50" t="s">
-        <v>11</v>
-      </c>
+      <c r="E38" s="50"/>
     </row>
     <row r="39" spans="1:5" ht="31.5" customHeight="1">
       <c r="A39" s="47">
         <v>37</v>
       </c>
-      <c r="B39" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="C39" s="48" t="s">
-        <v>26</v>
-      </c>
+      <c r="B39" s="48"/>
+      <c r="C39" s="48"/>
       <c r="D39" s="49"/>
-      <c r="E39" s="50" t="s">
-        <v>11</v>
-      </c>
+      <c r="E39" s="50"/>
     </row>
     <row r="40" spans="1:5" ht="31.5" customHeight="1">
       <c r="A40" s="47">
         <v>38</v>
       </c>
-      <c r="B40" s="48" t="s">
-        <v>108</v>
-      </c>
-      <c r="C40" s="48" t="s">
-        <v>27</v>
-      </c>
+      <c r="B40" s="48"/>
+      <c r="C40" s="48"/>
       <c r="D40" s="49"/>
-      <c r="E40" s="50" t="s">
-        <v>11</v>
-      </c>
+      <c r="E40" s="50"/>
     </row>
     <row r="41" spans="1:5" ht="31.5" customHeight="1">
       <c r="A41" s="47">
         <v>39</v>
       </c>
-      <c r="B41" s="48" t="s">
-        <v>62</v>
-      </c>
-      <c r="C41" s="48" t="s">
-        <v>28</v>
-      </c>
+      <c r="B41" s="48"/>
+      <c r="C41" s="48"/>
       <c r="D41" s="49"/>
-      <c r="E41" s="50" t="s">
-        <v>11</v>
-      </c>
+      <c r="E41" s="50"/>
     </row>
     <row r="42" spans="1:5" ht="31.5" customHeight="1">
       <c r="A42" s="47">
         <v>40</v>
       </c>
-      <c r="B42" s="48" t="s">
-        <v>80</v>
-      </c>
-      <c r="C42" s="48" t="s">
-        <v>27</v>
-      </c>
+      <c r="B42" s="48"/>
+      <c r="C42" s="48"/>
       <c r="D42" s="49"/>
-      <c r="E42" s="50" t="s">
-        <v>11</v>
-      </c>
+      <c r="E42" s="50"/>
     </row>
     <row r="43" spans="1:5" ht="31.5" customHeight="1">
       <c r="A43" s="47">
         <v>41</v>
       </c>
-      <c r="B43" s="48" t="s">
-        <v>83</v>
-      </c>
-      <c r="C43" s="48" t="s">
-        <v>26</v>
-      </c>
+      <c r="B43" s="48"/>
+      <c r="C43" s="48"/>
       <c r="D43" s="49"/>
-      <c r="E43" s="50" t="s">
-        <v>11</v>
-      </c>
+      <c r="E43" s="50"/>
     </row>
     <row r="44" spans="1:5" ht="31.5" customHeight="1">
       <c r="A44" s="51">
         <v>42</v>
       </c>
-      <c r="B44" s="52" t="s">
-        <v>84</v>
-      </c>
-      <c r="C44" s="52" t="s">
-        <v>26</v>
-      </c>
+      <c r="B44" s="52"/>
+      <c r="C44" s="52"/>
       <c r="D44" s="53"/>
-      <c r="E44" s="54" t="s">
-        <v>11</v>
-      </c>
+      <c r="E44" s="54"/>
     </row>
     <row r="45" spans="1:5" ht="31.5" customHeight="1">
       <c r="A45" s="47">
         <v>43</v>
       </c>
-      <c r="B45" s="48" t="s">
-        <v>89</v>
-      </c>
-      <c r="C45" s="48" t="s">
-        <v>26</v>
-      </c>
+      <c r="B45" s="48"/>
+      <c r="C45" s="48"/>
       <c r="D45" s="49"/>
-      <c r="E45" s="50" t="s">
-        <v>11</v>
-      </c>
+      <c r="E45" s="50"/>
     </row>
     <row r="46" spans="1:5" ht="31.5" customHeight="1">
       <c r="A46" s="47">
         <v>44</v>
       </c>
-      <c r="B46" s="48" t="s">
-        <v>93</v>
-      </c>
-      <c r="C46" s="48" t="s">
-        <v>26</v>
-      </c>
+      <c r="B46" s="48"/>
+      <c r="C46" s="48"/>
       <c r="D46" s="49"/>
-      <c r="E46" s="50" t="s">
-        <v>11</v>
-      </c>
+      <c r="E46" s="50"/>
     </row>
     <row r="47" spans="1:5" ht="31.5" customHeight="1">
       <c r="A47" s="47">
         <v>45</v>
       </c>
-      <c r="B47" s="48" t="s">
-        <v>78</v>
-      </c>
-      <c r="C47" s="48" t="s">
-        <v>27</v>
-      </c>
+      <c r="B47" s="48"/>
+      <c r="C47" s="48"/>
       <c r="D47" s="49"/>
-      <c r="E47" s="50" t="s">
-        <v>36</v>
-      </c>
+      <c r="E47" s="50"/>
     </row>
     <row r="48" spans="1:5" ht="31.5" customHeight="1">
       <c r="A48" s="47">
         <v>46</v>
       </c>
-      <c r="B48" s="48" t="s">
-        <v>106</v>
-      </c>
-      <c r="C48" s="48" t="s">
-        <v>27</v>
-      </c>
+      <c r="B48" s="48"/>
+      <c r="C48" s="48"/>
       <c r="D48" s="49"/>
-      <c r="E48" s="55" t="s">
-        <v>54</v>
-      </c>
+      <c r="E48" s="55"/>
     </row>
     <row r="49" spans="1:5" ht="31.5" customHeight="1">
       <c r="A49" s="47">
         <v>47</v>
       </c>
-      <c r="B49" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="C49" s="48" t="s">
-        <v>27</v>
-      </c>
+      <c r="B49" s="48"/>
+      <c r="C49" s="48"/>
       <c r="D49" s="49"/>
-      <c r="E49" s="55" t="s">
-        <v>54</v>
-      </c>
+      <c r="E49" s="55"/>
     </row>
     <row r="50" spans="1:5" ht="31.5" customHeight="1">
       <c r="A50" s="47">
         <v>48</v>
       </c>
-      <c r="B50" s="48" t="s">
-        <v>86</v>
-      </c>
-      <c r="C50" s="48" t="s">
-        <v>27</v>
-      </c>
+      <c r="B50" s="48"/>
+      <c r="C50" s="48"/>
       <c r="D50" s="49"/>
-      <c r="E50" s="55" t="s">
-        <v>54</v>
-      </c>
+      <c r="E50" s="55"/>
     </row>
     <row r="51" spans="1:5" ht="31.5" customHeight="1">
       <c r="A51" s="47">
         <v>49</v>
       </c>
-      <c r="B51" s="48" t="s">
-        <v>67</v>
-      </c>
-      <c r="C51" s="48" t="s">
-        <v>27</v>
-      </c>
+      <c r="B51" s="48"/>
+      <c r="C51" s="48"/>
       <c r="D51" s="49"/>
-      <c r="E51" s="55" t="s">
-        <v>54</v>
-      </c>
+      <c r="E51" s="55"/>
     </row>
     <row r="52" spans="1:5" ht="31.5" customHeight="1">
       <c r="A52" s="47">
         <v>50</v>
       </c>
-      <c r="B52" s="48" t="s">
-        <v>97</v>
-      </c>
-      <c r="C52" s="48" t="s">
-        <v>27</v>
-      </c>
+      <c r="B52" s="48"/>
+      <c r="C52" s="48"/>
       <c r="D52" s="49"/>
-      <c r="E52" s="50" t="s">
-        <v>59</v>
-      </c>
+      <c r="E52" s="50"/>
     </row>
   </sheetData>
   <autoFilter ref="E1:E52" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
@@ -3985,232 +3383,136 @@
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>7</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>9</v>
       </c>
       <c r="E1" s="19"/>
       <c r="F1" s="10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="10">
-        <v>10</v>
-      </c>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="10"/>
       <c r="E2" s="20"/>
-      <c r="F2" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="F2" s="4"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D3" s="10">
-        <v>10</v>
-      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="10"/>
       <c r="E3" s="20"/>
-      <c r="F3" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="F3" s="4"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D4" s="10">
-        <v>6</v>
-      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="10"/>
       <c r="E4" s="20"/>
-      <c r="F4" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="33.6">
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="D5" s="10">
-        <v>3</v>
-      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="10"/>
       <c r="E5" s="19"/>
-      <c r="F5" s="7" t="s">
-        <v>21</v>
-      </c>
+      <c r="F5" s="7"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="10">
-        <v>4</v>
-      </c>
+      <c r="B6" s="26"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="10"/>
       <c r="E6" s="19"/>
-      <c r="F6" s="4" t="s">
-        <v>30</v>
-      </c>
+      <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="10">
-        <v>2</v>
-      </c>
-      <c r="E7" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>35</v>
-      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="4"/>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="10">
-        <v>1</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>40</v>
-      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="4"/>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="10">
-        <v>1</v>
-      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="10"/>
       <c r="E9" s="19"/>
-      <c r="F9" s="4" t="s">
-        <v>41</v>
-      </c>
+      <c r="F9" s="4"/>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="4">
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="10">
-        <v>4</v>
-      </c>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="10"/>
       <c r="E10" s="19"/>
-      <c r="F10" s="4" t="s">
-        <v>48</v>
-      </c>
+      <c r="F10" s="4"/>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="4">
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>50</v>
-      </c>
+      <c r="B11" s="6"/>
       <c r="C11" s="6"/>
-      <c r="D11" s="10">
-        <v>3</v>
-      </c>
+      <c r="D11" s="10"/>
       <c r="E11" s="19"/>
-      <c r="F11" s="4" t="s">
-        <v>49</v>
-      </c>
+      <c r="F11" s="4"/>
     </row>
     <row r="12" spans="1:7" ht="21.75" customHeight="1">
       <c r="A12" s="4">
         <v>11</v>
       </c>
-      <c r="B12" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="D12" s="10">
-        <v>3</v>
-      </c>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="10"/>
       <c r="E12" s="19"/>
-      <c r="F12" s="7" t="s">
-        <v>22</v>
-      </c>
+      <c r="F12" s="7"/>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="4">
         <v>12</v>
       </c>
-      <c r="B13" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="10">
-        <v>1</v>
-      </c>
+      <c r="B13" s="26"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="10"/>
       <c r="E13" s="19"/>
       <c r="F13" s="7"/>
     </row>
@@ -4218,15 +3520,9 @@
       <c r="A14" s="4">
         <v>13</v>
       </c>
-      <c r="B14" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="10">
-        <v>2</v>
-      </c>
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="10"/>
       <c r="E14" s="19"/>
       <c r="F14" s="7"/>
     </row>
@@ -4234,15 +3530,9 @@
       <c r="A15" s="4">
         <v>14</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="D15" s="10">
-        <v>1</v>
-      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="10"/>
       <c r="E15" s="19"/>
       <c r="F15" s="7"/>
     </row>
@@ -4250,29 +3540,18 @@
       <c r="A16" s="4">
         <v>15</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C16" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="D16" s="10">
-        <v>1</v>
-      </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="10"/>
       <c r="E16" s="19"/>
-      <c r="F16" s="7" t="s">
-        <v>58</v>
-      </c>
+      <c r="F16" s="7"/>
       <c r="G16" s="9"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
-      <c r="D17" s="18">
-        <f>SUM(D2:D16)</f>
-        <v>52</v>
-      </c>
+      <c r="D17" s="18"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
     </row>
